--- a/数据表/Datas/RarityConfig_稀有度配置.xlsx
+++ b/数据表/Datas/RarityConfig_稀有度配置.xlsx
@@ -1,10 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:dbsheet="http://web.wps.cn/et/2021/dbsheet" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\UnityProjects\Seek-Battle-Evacuate\数据表\Datas\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
   <bookViews>
-    <workbookView windowHeight="16080"/>
+    <workbookView windowWidth="24750" windowHeight="12080"/>
   </bookViews>
   <sheets>
     <sheet name="Data" sheetId="1" r:id="rId1"/>
@@ -95,43 +100,43 @@
     </font>
     <font>
       <sz val="12"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF006100"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF1F4E78"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF595959"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF9C0006"/>
-      <name val="PingFang SC Regular"/>
+      <name val="微软雅黑"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="12"/>
       <color rgb="FF202020"/>
-      <name val="Andale Mono"/>
+      <name val="Consolas"/>
       <charset val="134"/>
     </font>
     <font>
@@ -286,7 +291,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="37">
+  <fills count="35">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -338,18 +343,6 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -687,7 +680,7 @@
     </border>
   </borders>
   <cellStyleXfs count="50">
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
@@ -753,90 +746,90 @@
     <xf numFmtId="0" fontId="22" fillId="0" borderId="13" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="23" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="24" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="25" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="35" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="26" fillId="36" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="23" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="24" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="25" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="33" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="13">
+  <cellXfs count="14">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
@@ -844,6 +837,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="49" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
@@ -1349,97 +1343,98 @@
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="20" customHeight="1" outlineLevelCol="2"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5955882352941" style="2" customWidth="1"/>
-    <col min="3" max="3" width="25.7352941176471" style="2" customWidth="1"/>
+    <col min="2" max="2" width="13.5916666666667" style="2" customWidth="1"/>
+    <col min="3" max="3" width="25.7333333333333" style="2" customWidth="1"/>
+    <col min="4" max="16384" width="9" style="3"/>
   </cols>
   <sheetData>
     <row r="1" customHeight="1" spans="1:3">
-      <c r="A1" s="3" t="s">
+      <c r="A1" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="5" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="4" t="s">
+      <c r="C1" s="5" t="s">
         <v>2</v>
       </c>
     </row>
     <row r="2" customHeight="1" spans="1:3">
-      <c r="A2" s="5" t="s">
+      <c r="A2" s="6" t="s">
         <v>3</v>
       </c>
-      <c r="B2" s="6" t="s">
+      <c r="B2" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="C2" s="6" t="s">
+      <c r="C2" s="7" t="s">
         <v>5</v>
       </c>
     </row>
     <row r="3" customHeight="1" spans="1:3">
-      <c r="A3" s="7" t="s">
+      <c r="A3" s="8" t="s">
         <v>6</v>
       </c>
-      <c r="B3" s="8" t="s">
+      <c r="B3" s="9" t="s">
         <v>7</v>
       </c>
-      <c r="C3" s="8" t="s">
+      <c r="C3" s="9" t="s">
         <v>7</v>
       </c>
     </row>
     <row r="4" customHeight="1" spans="1:3">
-      <c r="A4" s="9" t="s">
+      <c r="A4" s="10" t="s">
         <v>8</v>
       </c>
-      <c r="B4" s="10" t="s">
+      <c r="B4" s="11" t="s">
         <v>9</v>
       </c>
-      <c r="C4" s="10" t="s">
+      <c r="C4" s="11" t="s">
         <v>10</v>
       </c>
     </row>
     <row r="5" customHeight="1" spans="1:3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12" t="s">
+      <c r="A5" s="12"/>
+      <c r="B5" s="13" t="s">
         <v>11</v>
       </c>
-      <c r="C5" s="12">
-        <v>200</v>
+      <c r="C5" s="13">
+        <v>1000</v>
       </c>
     </row>
     <row r="6" customHeight="1" spans="1:3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12" t="s">
+      <c r="A6" s="12"/>
+      <c r="B6" s="13" t="s">
         <v>12</v>
       </c>
-      <c r="C6" s="12">
-        <v>400</v>
+      <c r="C6" s="13">
+        <v>1500</v>
       </c>
     </row>
     <row r="7" customHeight="1" spans="1:3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12" t="s">
+      <c r="A7" s="12"/>
+      <c r="B7" s="13" t="s">
         <v>13</v>
       </c>
-      <c r="C7" s="12">
-        <v>600</v>
+      <c r="C7" s="13">
+        <v>2000</v>
       </c>
     </row>
     <row r="8" customHeight="1" spans="1:3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12" t="s">
+      <c r="A8" s="12"/>
+      <c r="B8" s="13" t="s">
         <v>14</v>
       </c>
-      <c r="C8" s="12">
-        <v>800</v>
+      <c r="C8" s="13">
+        <v>3000</v>
       </c>
     </row>
     <row r="9" customHeight="1" spans="1:3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12" t="s">
+      <c r="A9" s="12"/>
+      <c r="B9" s="13" t="s">
         <v>15</v>
       </c>
-      <c r="C9" s="12">
-        <v>1000</v>
+      <c r="C9" s="13">
+        <v>4000</v>
       </c>
     </row>
   </sheetData>
